--- a/order_forms/045_gourmet_ingredient_starter_pack_order_form--order_forms.xlsx
+++ b/order_forms/045_gourmet_ingredient_starter_pack_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>form_assigned_tool</t>
+          <t>form_assigned_tool_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Form Assigned Tool</t>
+          <t>Form Assigned Tool 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Form Description</t>
+          <t>Form Description 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'type1'}</t>
+          <t>type1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'type1'}</t>
+          <t>type1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'type2'}</t>
+          <t>type2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'type2'}</t>
+          <t>type2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'type3'}</t>
+          <t>type3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'type3'}</t>
+          <t>type3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'category_1'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Category 1'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'category_2'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Category 2'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'category_3'}</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Category 3'}</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
